--- a/results/LM FD x microclimatic gradients.xlsx
+++ b/results/LM FD x microclimatic gradients.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/espinosaclara_uniovi_es/Documents/IMIB/Softwares/GitHub/Germination_drivers/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive - Universidad de Oviedo\IMIB\Softwares\GitHub\Germination_drivers\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{BCE7AEE2-7CA3-4B7F-87A3-035B7920FC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{140A1653-C6CA-4D18-9B85-45C3F90696D6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59DE300-92A5-4975-93DE-3DB3F913E1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E2F4E602-5982-49DE-AF44-84CAAD4FA04A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="transformed variables" sheetId="2" r:id="rId1"/>
+    <sheet name="original variables" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="35">
   <si>
     <t>MEDITERRANEAN</t>
   </si>
@@ -111,6 +112,36 @@
   </si>
   <si>
     <t>* *      +FDD +FDiv</t>
+  </si>
+  <si>
+    <t>nbsp</t>
+  </si>
+  <si>
+    <t>RaoQ</t>
+  </si>
+  <si>
+    <t>marginal</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>* +elevation +Fric</t>
+  </si>
+  <si>
+    <t>** +FDD +Fric</t>
+  </si>
+  <si>
+    <t>** +elevation  -FDiv</t>
+  </si>
+  <si>
+    <t>* +elevation  +FDiv</t>
+  </si>
+  <si>
+    <t>*** +FDD +Fric</t>
+  </si>
+  <si>
+    <t>* *         +FDD +species</t>
   </si>
 </sst>
 </file>
@@ -538,6 +569,395 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75FF90E0-0468-41ED-A3C8-BC6B275A20EF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="8.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="I1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="I11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="I13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="J9:O9"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA0C46D-C39D-4020-ABB7-87DDC0583D8F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>

--- a/results/LM FD x microclimatic gradients.xlsx
+++ b/results/LM FD x microclimatic gradients.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive - Universidad de Oviedo\IMIB\Softwares\GitHub\Germination_drivers\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioviedo-my.sharepoint.com/personal/espinosaclara_uniovi_es/Documents/IMIB/Softwares/GitHub/Germination_drivers/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59DE300-92A5-4975-93DE-3DB3F913E1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{F59DE300-92A5-4975-93DE-3DB3F913E1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9872DCE-DB66-48D6-8570-FE3DC5E8381E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E2F4E602-5982-49DE-AF44-84CAAD4FA04A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{E2F4E602-5982-49DE-AF44-84CAAD4FA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="transformed variables" sheetId="2" r:id="rId1"/>
@@ -251,6 +251,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -698,59 +702,61 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="I5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="2"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -759,12 +765,10 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -867,74 +871,74 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="M13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -953,7 +957,7 @@
     <mergeCell ref="J9:O9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="87" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1092,55 +1096,55 @@
       </c>
       <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1149,7 +1153,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1257,75 +1261,75 @@
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>24</v>
-      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="2"/>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="C13" s="2"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="G13" s="2"/>
       <c r="I13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>5</v>
-      </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="M14" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
     </row>
